--- a/etf_holdings/2026-10-20_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.73%753,000</t>
+          <t>9.76%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.73%</t>
+          <t>9.76%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4205</v>
+        <v>4150</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.65%249,000</t>
+          <t>5.61%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>5.61%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5125</v>
+        <v>4945</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.58%166,000</t>
+          <t>4.55%166,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.35%9920</t>
+          <t>+1.81%10100</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9920</v>
+        <v>10100</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.14%303.5</t>
+          <t>-2.47%296</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>303.5</v>
+        <v>296</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.96%2,416,000</t>
+          <t>3.93%2,416,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.53%6560</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6560</v>
+        <v>1055</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.74%104,000</t>
+          <t>3.75%625,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>104000</v>
+        <v>625000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.75%1120</t>
+          <t>+1.37%6650</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1120</v>
+        <v>6650</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.64%625,000</t>
+          <t>3.65%104,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>625000</v>
+        <v>104000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.31%1640</t>
+          <t>-2.13%1605</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1640</v>
+        <v>1605</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.53%404,000</t>
+          <t>3.55%404,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.18%5400</t>
+          <t>-3.61%5205</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5400</v>
+        <v>5205</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.91%103,000</t>
+          <t>2.98%103,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.57%436</t>
+          <t>-3.21%422</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.62%1,096,000</t>
+          <t>2.56%1,096,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>-1.09%7745</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3320</v>
+        <v>7745</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.37%134,000</t>
+          <t>2.47%59,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>134000</v>
+        <v>59000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.68%7830</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+4.68%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7830</v>
+        <v>3325</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.36%59,000</t>
+          <t>2.38%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>59000</v>
+        <v>134000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.4%1250</t>
+          <t>-5.2%1185</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1250</v>
+        <v>1185</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.24%337,000</t>
+          <t>2.26%337,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.22%621,000</t>
+          <t>2.23%621,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:21</t>
+          <t>2026-10-20 21:52:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.98%2570</t>
+          <t>-3.11%2490</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2570</v>
+        <v>2490</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.19%161,600</t>
+          <t>2.22%161,600</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.84%239.5</t>
+          <t>+0.84%241.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>239.5</v>
+        <v>241.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.10%1,616,000</t>
+          <t>2.07%1,616,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.58%5235</t>
+          <t>-6.4%4900</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5235</v>
+        <v>4900</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.06%74,000</t>
+          <t>2.07%74,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.72%155.5</t>
+          <t>-1.93%152.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>155.5</v>
+        <v>152.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.98%2,293,000</t>
+          <t>1.91%2,293,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.85%1380</t>
+          <t>-5.43%1305</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1380</v>
+        <v>1305</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.82%251,000</t>
+          <t>1.85%251,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-3.03%15980</t>
+          <t>-0.5%15900</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15980</v>
+        <v>15900</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.79%20,300</t>
+          <t>1.74%20,300</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,25 +1724,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.38%1845</t>
+          <t>-3.88%4960</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1845</v>
+        <v>4960</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.69%168,000</t>
+          <t>1.69%61,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1751,11 +1751,11 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>168000</v>
+        <v>61000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0%5160</t>
+          <t>0%1845</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1799,20 +1799,20 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5160</v>
+        <v>1845</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.68%61,000</t>
+          <t>1.66%168,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>61000</v>
+        <v>168000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.25%2005</t>
+          <t>-0.25%2000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.58%148,000</t>
+          <t>1.59%148,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1885</v>
+        <v>1925</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.53%155,105</t>
+          <t>1.57%155,105</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+1.26%2005</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2005</v>
+        <v>1970</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.50%142,000</t>
+          <t>1.52%142,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5.82%534</t>
+          <t>-3.77%945</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>534</v>
+        <v>945</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.47%485,000</t>
+          <t>1.40%266,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>485000</v>
+        <v>266000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,34 +2090,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.8%982</t>
+          <t>-2.06%523</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>982</v>
+        <v>523</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.42%266,000</t>
+          <t>1.39%485,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>266000</v>
+        <v>485000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6245</v>
+        <v>5975</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.30%38,000</t>
+          <t>1.27%38,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-8.81%735</t>
+          <t>-4.91%1550</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.81%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>735</v>
+        <v>1550</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.23%286,000</t>
+          <t>1.25%143,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>286000</v>
+        <v>143000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:22</t>
+          <t>2026-10-20 21:52:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.33%314.5</t>
+          <t>+1.91%320.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>314.5</v>
+        <v>320.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.23%718,000</t>
+          <t>1.21%718,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.93%1630</t>
+          <t>+8.03%794</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+8.03%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1630</v>
+        <v>794</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.23%143,000</t>
+          <t>1.13%286,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>143000</v>
+        <v>286000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.27%73.4</t>
+          <t>-2.45%71.6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>73.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.13%131.5</t>
+          <t>-3.42%127</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>131.5</v>
+        <v>127</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.05%1,474,000</t>
+          <t>1.04%1,474,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.9%767</t>
+          <t>-2.35%749</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.04%252,000</t>
+          <t>1.03%252,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.14%205.5</t>
+          <t>+0.97%207.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>205.5</v>
+        <v>207.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.02%906,000</t>
+          <t>1.00%906,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.37%180</t>
+          <t>+5%189</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.92%948,000</t>
+          <t>0.91%948,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.54%352</t>
+          <t>+0.85%355</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.92%484,000</t>
+          <t>0.91%484,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.19%258</t>
+          <t>-4.26%247</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-4.26%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.49%72.8</t>
+          <t>+0.27%73</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>72.8</v>
+        <v>73</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.89%2,255,500</t>
+          <t>0.88%2,255,500</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.64%774</t>
+          <t>+1.16%783</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.87%204,000</t>
+          <t>0.85%204,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.41%49.35</t>
+          <t>-2.03%48.35</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>49.35</v>
+        <v>48.35</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.23%1500</t>
+          <t>-4.33%1435</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.23%</t>
+          <t>-4.33%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1500</v>
+        <v>1435</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.75%91,000</t>
+          <t>0.73%91,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+3.78%2335</t>
+          <t>-1.93%2290</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2335</v>
+        <v>2290</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.65%54,000</t>
+          <t>0.68%54,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2%2695</t>
+          <t>-1.48%2655</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2695</v>
+        <v>2655</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.65%44,000</t>
+          <t>0.63%44,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:23</t>
+          <t>2026-10-20 21:52:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.2%577</t>
+          <t>-1.73%567</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.61%195,000</t>
+          <t>0.60%195,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:25</t>
+          <t>2026-10-20 21:52:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.99%1975</t>
+          <t>-2.53%1925</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1975</v>
+        <v>1925</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.52%48,336</t>
+          <t>0.51%48,336</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:25</t>
+          <t>2026-10-20 21:52:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.87%1525</t>
+          <t>+1.31%1545</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1525</v>
+        <v>1545</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.49%58,000</t>
+          <t>0.47%58,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:25</t>
+          <t>2026-10-20 21:52:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.52%813</t>
+          <t>-1.48%801</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.42%95,000</t>
+          <t>0.41%95,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:25</t>
+          <t>2026-10-20 21:52:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.86%407.5</t>
+          <t>+0.49%409.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.86%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>407.5</v>
+        <v>409.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.41%182,000</t>
+          <t>0.40%182,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:25</t>
+          <t>2026-10-20 21:52:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,25 +3498,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.66%1495</t>
+          <t>-2.68%1455</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1495</v>
+        <v>1455</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.31%38,000</t>
+          <t>0.30%38,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-20_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:02</t>
+          <t>2026-10-20 22:18:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:03</t>
+          <t>2026-10-20 22:18:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:05</t>
+          <t>2026-10-20 22:18:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:06</t>
+          <t>2026-10-20 22:18:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:06</t>
+          <t>2026-10-20 22:18:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:06</t>
+          <t>2026-10-20 22:18:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:06</t>
+          <t>2026-10-20 22:18:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:52:06</t>
+          <t>2026-10-20 22:18:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
